--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4137-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4137-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5403730C-A117-4211-B454-133E6717C943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CDB0731-95F4-4C6A-9163-56631C55141F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{036EB842-D633-412D-ACA8-F5AB2C393EE3}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{CB434C9A-05AE-4F20-9267-50C8EEB034F1}"/>
   </bookViews>
   <sheets>
     <sheet name="4137-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1430,23 +1430,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC28791-7CA6-4AA1-9CB5-09BFB444B37A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC8077CF-93A0-4BC9-A859-631A802F82F9}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="7.5" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1474,7 +1474,7 @@
       <c r="Q1" s="28"/>
       <c r="R1" s="20"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1504,7 +1504,7 @@
       <c r="Q2" s="30"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1600,7 +1600,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>8.23</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>8.23</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>2024</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2022</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>6.14</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="35">
         <v>2021</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>2020</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="35">
         <v>2019</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2018</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="35">
         <v>2017</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2016</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="35">
         <v>2015</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2014</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="35">
         <v>2013</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
         <v>31</v>
       </c>
